--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D5F541-AA8C-431B-8F80-1150AA58D3F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55556C59-BE2B-43F1-870D-ADA8DCF439B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="77895" yWindow="960" windowWidth="17280" windowHeight="18765" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="58095" yWindow="3090" windowWidth="21585" windowHeight="17475" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="+ MILIONÁRIA" sheetId="12" r:id="rId1"/>
@@ -109,13 +109,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -436,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2F70E5-30B2-4963-A61E-AD5ABF761887}">
-  <dimension ref="A1:I329"/>
+  <dimension ref="A1:I332"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.84375" bestFit="1" customWidth="1"/>
@@ -9872,119 +9870,206 @@
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A326" s="2">
+      <c r="A326">
         <v>325</v>
       </c>
-      <c r="B326" s="3">
+      <c r="B326">
         <v>13</v>
       </c>
-      <c r="C326" s="3">
+      <c r="C326">
         <v>14</v>
       </c>
-      <c r="D326" s="3">
+      <c r="D326">
         <v>19</v>
       </c>
-      <c r="E326" s="3">
+      <c r="E326">
         <v>21</v>
       </c>
-      <c r="F326" s="3">
+      <c r="F326">
         <v>26</v>
       </c>
-      <c r="G326" s="3">
+      <c r="G326">
         <v>41</v>
       </c>
-      <c r="H326" s="3">
-        <v>4</v>
-      </c>
-      <c r="I326" s="3">
+      <c r="H326">
+        <v>4</v>
+      </c>
+      <c r="I326">
         <v>5</v>
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A327" s="2">
+      <c r="A327">
         <v>326</v>
       </c>
-      <c r="B327" s="3">
+      <c r="B327">
         <v>16</v>
       </c>
-      <c r="C327" s="3">
+      <c r="C327">
         <v>20</v>
       </c>
-      <c r="D327" s="3">
+      <c r="D327">
         <v>29</v>
       </c>
-      <c r="E327" s="3">
+      <c r="E327">
         <v>34</v>
       </c>
-      <c r="F327" s="3">
+      <c r="F327">
         <v>35</v>
       </c>
-      <c r="G327" s="3">
+      <c r="G327">
         <v>42</v>
       </c>
-      <c r="H327" s="3">
-        <v>3</v>
-      </c>
-      <c r="I327" s="3">
+      <c r="H327">
+        <v>3</v>
+      </c>
+      <c r="I327">
         <v>5</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A328" s="2">
+      <c r="A328">
         <v>327</v>
       </c>
-      <c r="B328" s="3">
-        <v>4</v>
-      </c>
-      <c r="C328" s="3">
+      <c r="B328">
+        <v>4</v>
+      </c>
+      <c r="C328">
         <v>7</v>
       </c>
-      <c r="D328" s="3">
+      <c r="D328">
         <v>12</v>
       </c>
-      <c r="E328" s="3">
+      <c r="E328">
         <v>25</v>
       </c>
-      <c r="F328" s="3">
+      <c r="F328">
         <v>28</v>
       </c>
-      <c r="G328" s="3">
+      <c r="G328">
         <v>46</v>
       </c>
-      <c r="H328" s="3">
-        <v>1</v>
-      </c>
-      <c r="I328" s="3">
+      <c r="H328">
+        <v>1</v>
+      </c>
+      <c r="I328">
         <v>2</v>
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A329" s="2">
+      <c r="A329">
         <v>328</v>
       </c>
-      <c r="B329" s="3">
-        <v>3</v>
-      </c>
-      <c r="C329" s="3">
+      <c r="B329">
+        <v>3</v>
+      </c>
+      <c r="C329">
         <v>19</v>
       </c>
-      <c r="D329" s="3">
+      <c r="D329">
         <v>21</v>
       </c>
-      <c r="E329" s="3">
+      <c r="E329">
         <v>25</v>
       </c>
-      <c r="F329" s="3">
+      <c r="F329">
         <v>27</v>
       </c>
-      <c r="G329" s="3">
+      <c r="G329">
         <v>42</v>
       </c>
-      <c r="H329" s="3">
-        <v>2</v>
-      </c>
-      <c r="I329" s="3">
-        <v>3</v>
+      <c r="H329">
+        <v>2</v>
+      </c>
+      <c r="I329">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A330">
+        <v>329</v>
+      </c>
+      <c r="B330">
+        <v>12</v>
+      </c>
+      <c r="C330">
+        <v>13</v>
+      </c>
+      <c r="D330">
+        <v>15</v>
+      </c>
+      <c r="E330">
+        <v>22</v>
+      </c>
+      <c r="F330">
+        <v>23</v>
+      </c>
+      <c r="G330">
+        <v>49</v>
+      </c>
+      <c r="H330">
+        <v>2</v>
+      </c>
+      <c r="I330">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A331">
+        <v>330</v>
+      </c>
+      <c r="B331">
+        <v>4</v>
+      </c>
+      <c r="C331">
+        <v>13</v>
+      </c>
+      <c r="D331">
+        <v>25</v>
+      </c>
+      <c r="E331">
+        <v>33</v>
+      </c>
+      <c r="F331">
+        <v>41</v>
+      </c>
+      <c r="G331">
+        <v>49</v>
+      </c>
+      <c r="H331">
+        <v>3</v>
+      </c>
+      <c r="I331">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A332">
+        <v>331</v>
+      </c>
+      <c r="B332">
+        <v>4</v>
+      </c>
+      <c r="C332">
+        <v>12</v>
+      </c>
+      <c r="D332">
+        <v>18</v>
+      </c>
+      <c r="E332">
+        <v>23</v>
+      </c>
+      <c r="F332">
+        <v>39</v>
+      </c>
+      <c r="G332">
+        <v>44</v>
+      </c>
+      <c r="H332">
+        <v>1</v>
+      </c>
+      <c r="I332">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -9994,12 +10079,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10171,19 +10257,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10209,12 +10297,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55556C59-BE2B-43F1-870D-ADA8DCF439B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050933A2-C2F7-4492-81E4-490E5F3224DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58095" yWindow="3090" windowWidth="21585" windowHeight="17475" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="59805" yWindow="2205" windowWidth="19485" windowHeight="18465" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="+ MILIONÁRIA" sheetId="12" r:id="rId1"/>
@@ -109,11 +109,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,17 +436,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2F70E5-30B2-4963-A61E-AD5ABF761887}">
-  <dimension ref="A1:I332"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:I344"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.84375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="5.84375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.4609375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.69140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.53125" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="5.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.46484375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -473,7 +475,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
@@ -502,7 +504,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
@@ -531,7 +533,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
       </c>
@@ -560,7 +562,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>4</v>
       </c>
@@ -589,7 +591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>5</v>
       </c>
@@ -618,7 +620,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>6</v>
       </c>
@@ -647,7 +649,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>7</v>
       </c>
@@ -676,7 +678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>8</v>
       </c>
@@ -705,7 +707,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>9</v>
       </c>
@@ -734,7 +736,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>10</v>
       </c>
@@ -763,7 +765,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>11</v>
       </c>
@@ -792,7 +794,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>12</v>
       </c>
@@ -821,7 +823,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>13</v>
       </c>
@@ -850,7 +852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>14</v>
       </c>
@@ -879,7 +881,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>15</v>
       </c>
@@ -908,7 +910,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>16</v>
       </c>
@@ -937,7 +939,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>17</v>
       </c>
@@ -966,7 +968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>18</v>
       </c>
@@ -995,7 +997,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1024,7 +1026,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1053,7 +1055,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1082,7 +1084,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1111,7 +1113,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1140,7 +1142,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1169,7 +1171,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1198,7 +1200,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1227,7 +1229,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1256,7 +1258,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1285,7 +1287,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1314,7 +1316,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1343,7 +1345,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1372,7 +1374,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1401,7 +1403,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1430,7 +1432,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1459,7 +1461,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1488,7 +1490,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1517,7 +1519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1546,7 +1548,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1575,7 +1577,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1604,7 +1606,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1633,7 +1635,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1662,7 +1664,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1691,7 +1693,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1720,7 +1722,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1749,7 +1751,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1778,7 +1780,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1807,7 +1809,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1836,7 +1838,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1865,7 +1867,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1894,7 +1896,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1923,7 +1925,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1952,7 +1954,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1981,7 +1983,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2010,7 +2012,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2039,7 +2041,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2068,7 +2070,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2097,7 +2099,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2126,7 +2128,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2155,7 +2157,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2184,7 +2186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2213,7 +2215,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2242,7 +2244,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2271,7 +2273,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2300,7 +2302,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2329,7 +2331,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2358,7 +2360,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2387,7 +2389,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2416,7 +2418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2445,7 +2447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2474,7 +2476,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2503,7 +2505,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2532,7 +2534,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2561,7 +2563,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2590,7 +2592,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>74</v>
       </c>
@@ -2619,7 +2621,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>75</v>
       </c>
@@ -2648,7 +2650,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>76</v>
       </c>
@@ -2677,7 +2679,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>77</v>
       </c>
@@ -2706,7 +2708,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>78</v>
       </c>
@@ -2735,7 +2737,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>79</v>
       </c>
@@ -2764,7 +2766,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>80</v>
       </c>
@@ -2793,7 +2795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>81</v>
       </c>
@@ -2822,7 +2824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>82</v>
       </c>
@@ -2851,7 +2853,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>83</v>
       </c>
@@ -2880,7 +2882,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>84</v>
       </c>
@@ -2909,7 +2911,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>85</v>
       </c>
@@ -2938,7 +2940,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>86</v>
       </c>
@@ -2967,7 +2969,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>87</v>
       </c>
@@ -2996,7 +2998,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>88</v>
       </c>
@@ -3025,7 +3027,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>89</v>
       </c>
@@ -3054,7 +3056,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>90</v>
       </c>
@@ -3083,7 +3085,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>91</v>
       </c>
@@ -3112,7 +3114,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>92</v>
       </c>
@@ -3141,7 +3143,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>93</v>
       </c>
@@ -3170,7 +3172,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>94</v>
       </c>
@@ -3199,7 +3201,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>95</v>
       </c>
@@ -3228,7 +3230,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>96</v>
       </c>
@@ -3257,7 +3259,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>97</v>
       </c>
@@ -3286,7 +3288,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>98</v>
       </c>
@@ -3315,7 +3317,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>99</v>
       </c>
@@ -3344,7 +3346,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>100</v>
       </c>
@@ -3373,7 +3375,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>101</v>
       </c>
@@ -3402,7 +3404,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>102</v>
       </c>
@@ -3431,7 +3433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>103</v>
       </c>
@@ -3460,7 +3462,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>104</v>
       </c>
@@ -3489,7 +3491,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>105</v>
       </c>
@@ -3518,7 +3520,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>106</v>
       </c>
@@ -3547,7 +3549,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>107</v>
       </c>
@@ -3576,7 +3578,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>108</v>
       </c>
@@ -3605,7 +3607,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>109</v>
       </c>
@@ -3634,7 +3636,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>110</v>
       </c>
@@ -3663,7 +3665,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>111</v>
       </c>
@@ -3692,7 +3694,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>112</v>
       </c>
@@ -3721,7 +3723,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>113</v>
       </c>
@@ -3750,7 +3752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>114</v>
       </c>
@@ -3779,7 +3781,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>115</v>
       </c>
@@ -3808,7 +3810,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>116</v>
       </c>
@@ -3837,7 +3839,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A118">
         <v>117</v>
       </c>
@@ -3866,7 +3868,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A119">
         <v>118</v>
       </c>
@@ -3895,7 +3897,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A120">
         <v>119</v>
       </c>
@@ -3924,7 +3926,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A121">
         <v>120</v>
       </c>
@@ -3953,7 +3955,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A122">
         <v>121</v>
       </c>
@@ -3982,7 +3984,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A123">
         <v>122</v>
       </c>
@@ -4011,7 +4013,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A124">
         <v>123</v>
       </c>
@@ -4040,7 +4042,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A125">
         <v>124</v>
       </c>
@@ -4069,7 +4071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A126">
         <v>125</v>
       </c>
@@ -4098,7 +4100,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A127">
         <v>126</v>
       </c>
@@ -4127,7 +4129,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A128">
         <v>127</v>
       </c>
@@ -4156,7 +4158,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A129">
         <v>128</v>
       </c>
@@ -4185,7 +4187,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>129</v>
       </c>
@@ -4214,7 +4216,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>130</v>
       </c>
@@ -4243,7 +4245,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>131</v>
       </c>
@@ -4272,7 +4274,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>132</v>
       </c>
@@ -4301,7 +4303,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A134">
         <v>133</v>
       </c>
@@ -4330,7 +4332,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A135">
         <v>134</v>
       </c>
@@ -4359,7 +4361,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A136">
         <v>135</v>
       </c>
@@ -4388,7 +4390,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A137">
         <v>136</v>
       </c>
@@ -4417,7 +4419,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A138">
         <v>137</v>
       </c>
@@ -4446,7 +4448,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A139">
         <v>138</v>
       </c>
@@ -4475,7 +4477,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A140">
         <v>139</v>
       </c>
@@ -4504,7 +4506,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A141">
         <v>140</v>
       </c>
@@ -4533,7 +4535,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A142">
         <v>141</v>
       </c>
@@ -4562,7 +4564,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A143">
         <v>142</v>
       </c>
@@ -4591,7 +4593,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A144">
         <v>143</v>
       </c>
@@ -4620,7 +4622,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A145">
         <v>144</v>
       </c>
@@ -4649,7 +4651,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A146">
         <v>145</v>
       </c>
@@ -4678,7 +4680,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A147">
         <v>146</v>
       </c>
@@ -4707,7 +4709,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A148">
         <v>147</v>
       </c>
@@ -4736,7 +4738,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A149">
         <v>148</v>
       </c>
@@ -4765,7 +4767,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A150">
         <v>149</v>
       </c>
@@ -4794,7 +4796,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A151">
         <v>150</v>
       </c>
@@ -4823,7 +4825,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A152">
         <v>151</v>
       </c>
@@ -4852,7 +4854,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A153">
         <v>152</v>
       </c>
@@ -4881,7 +4883,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A154">
         <v>153</v>
       </c>
@@ -4910,7 +4912,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A155">
         <v>154</v>
       </c>
@@ -4939,7 +4941,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A156">
         <v>155</v>
       </c>
@@ -4968,7 +4970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A157">
         <v>156</v>
       </c>
@@ -4997,7 +4999,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A158">
         <v>157</v>
       </c>
@@ -5026,7 +5028,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A159">
         <v>158</v>
       </c>
@@ -5055,7 +5057,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A160">
         <v>159</v>
       </c>
@@ -5084,7 +5086,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A161">
         <v>160</v>
       </c>
@@ -5113,7 +5115,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A162">
         <v>161</v>
       </c>
@@ -5142,7 +5144,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A163">
         <v>162</v>
       </c>
@@ -5171,7 +5173,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A164">
         <v>163</v>
       </c>
@@ -5200,7 +5202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A165">
         <v>164</v>
       </c>
@@ -5229,7 +5231,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A166">
         <v>165</v>
       </c>
@@ -5258,7 +5260,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A167">
         <v>166</v>
       </c>
@@ -5287,7 +5289,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A168">
         <v>167</v>
       </c>
@@ -5316,7 +5318,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A169">
         <v>168</v>
       </c>
@@ -5345,7 +5347,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A170">
         <v>169</v>
       </c>
@@ -5374,7 +5376,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A171">
         <v>170</v>
       </c>
@@ -5403,7 +5405,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A172">
         <v>171</v>
       </c>
@@ -5432,7 +5434,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A173">
         <v>172</v>
       </c>
@@ -5461,7 +5463,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A174">
         <v>173</v>
       </c>
@@ -5490,7 +5492,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A175">
         <v>174</v>
       </c>
@@ -5519,7 +5521,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A176">
         <v>175</v>
       </c>
@@ -5548,7 +5550,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A177">
         <v>176</v>
       </c>
@@ -5577,7 +5579,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A178">
         <v>177</v>
       </c>
@@ -5606,7 +5608,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A179">
         <v>178</v>
       </c>
@@ -5635,7 +5637,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A180">
         <v>179</v>
       </c>
@@ -5664,7 +5666,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A181">
         <v>180</v>
       </c>
@@ -5693,7 +5695,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A182">
         <v>181</v>
       </c>
@@ -5722,7 +5724,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A183">
         <v>182</v>
       </c>
@@ -5751,7 +5753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A184">
         <v>183</v>
       </c>
@@ -5780,7 +5782,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A185">
         <v>184</v>
       </c>
@@ -5809,7 +5811,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A186">
         <v>185</v>
       </c>
@@ -5838,7 +5840,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A187">
         <v>186</v>
       </c>
@@ -5867,7 +5869,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A188">
         <v>187</v>
       </c>
@@ -5896,7 +5898,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A189">
         <v>188</v>
       </c>
@@ -5925,7 +5927,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A190">
         <v>189</v>
       </c>
@@ -5954,7 +5956,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A191">
         <v>190</v>
       </c>
@@ -5983,7 +5985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A192">
         <v>191</v>
       </c>
@@ -6012,7 +6014,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A193">
         <v>192</v>
       </c>
@@ -6041,7 +6043,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A194">
         <v>193</v>
       </c>
@@ -6070,7 +6072,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A195">
         <v>194</v>
       </c>
@@ -6099,7 +6101,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A196">
         <v>195</v>
       </c>
@@ -6128,7 +6130,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A197">
         <v>196</v>
       </c>
@@ -6157,7 +6159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A198">
         <v>197</v>
       </c>
@@ -6186,7 +6188,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A199">
         <v>198</v>
       </c>
@@ -6215,7 +6217,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A200">
         <v>199</v>
       </c>
@@ -6244,7 +6246,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A201">
         <v>200</v>
       </c>
@@ -6273,7 +6275,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A202">
         <v>201</v>
       </c>
@@ -6302,7 +6304,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A203">
         <v>202</v>
       </c>
@@ -6331,7 +6333,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A204">
         <v>203</v>
       </c>
@@ -6360,7 +6362,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A205">
         <v>204</v>
       </c>
@@ -6389,7 +6391,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A206">
         <v>205</v>
       </c>
@@ -6418,7 +6420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A207">
         <v>206</v>
       </c>
@@ -6447,7 +6449,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A208">
         <v>207</v>
       </c>
@@ -6476,7 +6478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A209">
         <v>208</v>
       </c>
@@ -6505,7 +6507,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A210">
         <v>209</v>
       </c>
@@ -6534,7 +6536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A211">
         <v>210</v>
       </c>
@@ -6563,7 +6565,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A212">
         <v>211</v>
       </c>
@@ -6592,7 +6594,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A213">
         <v>212</v>
       </c>
@@ -6621,7 +6623,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A214">
         <v>213</v>
       </c>
@@ -6650,7 +6652,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A215">
         <v>214</v>
       </c>
@@ -6679,7 +6681,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A216">
         <v>215</v>
       </c>
@@ -6708,7 +6710,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A217">
         <v>216</v>
       </c>
@@ -6737,7 +6739,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A218">
         <v>217</v>
       </c>
@@ -6766,7 +6768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A219">
         <v>218</v>
       </c>
@@ -6795,7 +6797,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A220">
         <v>219</v>
       </c>
@@ -6824,7 +6826,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A221">
         <v>220</v>
       </c>
@@ -6853,7 +6855,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A222">
         <v>221</v>
       </c>
@@ -6882,7 +6884,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A223">
         <v>222</v>
       </c>
@@ -6911,7 +6913,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A224">
         <v>223</v>
       </c>
@@ -6940,7 +6942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A225">
         <v>224</v>
       </c>
@@ -6969,7 +6971,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A226">
         <v>225</v>
       </c>
@@ -6998,7 +7000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A227">
         <v>226</v>
       </c>
@@ -7027,7 +7029,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A228">
         <v>227</v>
       </c>
@@ -7056,7 +7058,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A229">
         <v>228</v>
       </c>
@@ -7085,7 +7087,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A230">
         <v>229</v>
       </c>
@@ -7114,7 +7116,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A231">
         <v>230</v>
       </c>
@@ -7143,7 +7145,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A232">
         <v>231</v>
       </c>
@@ -7172,7 +7174,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A233">
         <v>232</v>
       </c>
@@ -7201,7 +7203,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A234">
         <v>233</v>
       </c>
@@ -7230,7 +7232,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A235">
         <v>234</v>
       </c>
@@ -7259,7 +7261,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A236">
         <v>235</v>
       </c>
@@ -7288,7 +7290,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A237">
         <v>236</v>
       </c>
@@ -7317,7 +7319,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A238">
         <v>237</v>
       </c>
@@ -7346,7 +7348,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A239">
         <v>238</v>
       </c>
@@ -7375,7 +7377,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A240">
         <v>239</v>
       </c>
@@ -7404,7 +7406,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A241">
         <v>240</v>
       </c>
@@ -7433,7 +7435,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A242">
         <v>241</v>
       </c>
@@ -7462,7 +7464,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A243">
         <v>242</v>
       </c>
@@ -7491,7 +7493,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A244">
         <v>243</v>
       </c>
@@ -7520,7 +7522,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A245">
         <v>244</v>
       </c>
@@ -7549,7 +7551,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A246">
         <v>245</v>
       </c>
@@ -7578,7 +7580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A247">
         <v>246</v>
       </c>
@@ -7607,7 +7609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A248">
         <v>247</v>
       </c>
@@ -7636,7 +7638,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A249">
         <v>248</v>
       </c>
@@ -7665,7 +7667,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A250">
         <v>249</v>
       </c>
@@ -7694,7 +7696,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A251">
         <v>250</v>
       </c>
@@ -7723,7 +7725,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A252">
         <v>251</v>
       </c>
@@ -7752,7 +7754,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A253">
         <v>252</v>
       </c>
@@ -7781,7 +7783,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A254">
         <v>253</v>
       </c>
@@ -7810,7 +7812,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A255">
         <v>254</v>
       </c>
@@ -7839,7 +7841,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A256">
         <v>255</v>
       </c>
@@ -7868,7 +7870,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A257">
         <v>256</v>
       </c>
@@ -7897,7 +7899,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A258">
         <v>257</v>
       </c>
@@ -7926,7 +7928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A259">
         <v>258</v>
       </c>
@@ -7955,7 +7957,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A260">
         <v>259</v>
       </c>
@@ -7984,7 +7986,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A261">
         <v>260</v>
       </c>
@@ -8013,7 +8015,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A262">
         <v>261</v>
       </c>
@@ -8042,7 +8044,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A263">
         <v>262</v>
       </c>
@@ -8071,7 +8073,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A264">
         <v>263</v>
       </c>
@@ -8100,7 +8102,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A265">
         <v>264</v>
       </c>
@@ -8129,7 +8131,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A266">
         <v>265</v>
       </c>
@@ -8158,7 +8160,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A267">
         <v>266</v>
       </c>
@@ -8187,7 +8189,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A268">
         <v>267</v>
       </c>
@@ -8216,7 +8218,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A269">
         <v>268</v>
       </c>
@@ -8245,7 +8247,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A270">
         <v>269</v>
       </c>
@@ -8274,7 +8276,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A271">
         <v>270</v>
       </c>
@@ -8303,7 +8305,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A272">
         <v>271</v>
       </c>
@@ -8332,7 +8334,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A273">
         <v>272</v>
       </c>
@@ -8361,7 +8363,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A274">
         <v>273</v>
       </c>
@@ -8390,7 +8392,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A275">
         <v>274</v>
       </c>
@@ -8419,7 +8421,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A276">
         <v>275</v>
       </c>
@@ -8448,7 +8450,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A277">
         <v>276</v>
       </c>
@@ -8477,7 +8479,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A278">
         <v>277</v>
       </c>
@@ -8506,7 +8508,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A279">
         <v>278</v>
       </c>
@@ -8535,7 +8537,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A280">
         <v>279</v>
       </c>
@@ -8564,7 +8566,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A281">
         <v>280</v>
       </c>
@@ -8593,7 +8595,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A282">
         <v>281</v>
       </c>
@@ -8622,7 +8624,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A283">
         <v>282</v>
       </c>
@@ -8651,7 +8653,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A284">
         <v>283</v>
       </c>
@@ -8680,7 +8682,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A285">
         <v>284</v>
       </c>
@@ -8709,7 +8711,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A286">
         <v>285</v>
       </c>
@@ -8738,7 +8740,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A287">
         <v>286</v>
       </c>
@@ -8767,7 +8769,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A288">
         <v>287</v>
       </c>
@@ -8796,7 +8798,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A289">
         <v>288</v>
       </c>
@@ -8825,7 +8827,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A290">
         <v>289</v>
       </c>
@@ -8854,7 +8856,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A291">
         <v>290</v>
       </c>
@@ -8883,7 +8885,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A292">
         <v>291</v>
       </c>
@@ -8912,7 +8914,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A293">
         <v>292</v>
       </c>
@@ -8941,7 +8943,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A294">
         <v>293</v>
       </c>
@@ -8970,7 +8972,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A295">
         <v>294</v>
       </c>
@@ -8999,7 +9001,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A296">
         <v>295</v>
       </c>
@@ -9028,7 +9030,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A297">
         <v>296</v>
       </c>
@@ -9057,7 +9059,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A298">
         <v>297</v>
       </c>
@@ -9086,7 +9088,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A299">
         <v>298</v>
       </c>
@@ -9115,7 +9117,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A300">
         <v>299</v>
       </c>
@@ -9144,7 +9146,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A301">
         <v>300</v>
       </c>
@@ -9173,7 +9175,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A302">
         <v>301</v>
       </c>
@@ -9202,7 +9204,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A303">
         <v>302</v>
       </c>
@@ -9231,7 +9233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A304">
         <v>303</v>
       </c>
@@ -9260,7 +9262,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A305">
         <v>304</v>
       </c>
@@ -9289,7 +9291,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A306">
         <v>305</v>
       </c>
@@ -9318,7 +9320,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A307">
         <v>306</v>
       </c>
@@ -9347,7 +9349,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A308">
         <v>307</v>
       </c>
@@ -9376,7 +9378,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A309">
         <v>308</v>
       </c>
@@ -9405,7 +9407,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A310">
         <v>309</v>
       </c>
@@ -9434,7 +9436,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A311">
         <v>310</v>
       </c>
@@ -9463,7 +9465,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A312">
         <v>311</v>
       </c>
@@ -9492,7 +9494,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A313">
         <v>312</v>
       </c>
@@ -9521,7 +9523,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A314">
         <v>313</v>
       </c>
@@ -9550,7 +9552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A315">
         <v>314</v>
       </c>
@@ -9579,7 +9581,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A316">
         <v>315</v>
       </c>
@@ -9608,7 +9610,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A317">
         <v>316</v>
       </c>
@@ -9637,7 +9639,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A318">
         <v>317</v>
       </c>
@@ -9666,7 +9668,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A319">
         <v>318</v>
       </c>
@@ -9695,7 +9697,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A320">
         <v>319</v>
       </c>
@@ -9724,7 +9726,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A321">
         <v>320</v>
       </c>
@@ -9753,7 +9755,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A322">
         <v>321</v>
       </c>
@@ -9782,7 +9784,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A323">
         <v>322</v>
       </c>
@@ -9811,7 +9813,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A324">
         <v>323</v>
       </c>
@@ -9840,7 +9842,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A325">
         <v>324</v>
       </c>
@@ -9869,7 +9871,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A326">
         <v>325</v>
       </c>
@@ -9898,7 +9900,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A327">
         <v>326</v>
       </c>
@@ -9927,7 +9929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A328">
         <v>327</v>
       </c>
@@ -9956,7 +9958,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A329">
         <v>328</v>
       </c>
@@ -9985,7 +9987,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A330">
         <v>329</v>
       </c>
@@ -10014,7 +10016,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A331">
         <v>330</v>
       </c>
@@ -10043,7 +10045,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A332">
         <v>331</v>
       </c>
@@ -10069,6 +10071,354 @@
         <v>1</v>
       </c>
       <c r="I332">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A333" s="2">
+        <v>332</v>
+      </c>
+      <c r="B333" s="3">
+        <v>35</v>
+      </c>
+      <c r="C333" s="3">
+        <v>36</v>
+      </c>
+      <c r="D333" s="3">
+        <v>40</v>
+      </c>
+      <c r="E333" s="3">
+        <v>43</v>
+      </c>
+      <c r="F333" s="3">
+        <v>47</v>
+      </c>
+      <c r="G333" s="3">
+        <v>50</v>
+      </c>
+      <c r="H333" s="3">
+        <v>4</v>
+      </c>
+      <c r="I333" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A334" s="2">
+        <v>333</v>
+      </c>
+      <c r="B334" s="3">
+        <v>1</v>
+      </c>
+      <c r="C334" s="3">
+        <v>20</v>
+      </c>
+      <c r="D334" s="3">
+        <v>28</v>
+      </c>
+      <c r="E334" s="3">
+        <v>37</v>
+      </c>
+      <c r="F334" s="3">
+        <v>40</v>
+      </c>
+      <c r="G334" s="3">
+        <v>43</v>
+      </c>
+      <c r="H334" s="3">
+        <v>2</v>
+      </c>
+      <c r="I334" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A335" s="2">
+        <v>334</v>
+      </c>
+      <c r="B335" s="3">
+        <v>25</v>
+      </c>
+      <c r="C335" s="3">
+        <v>44</v>
+      </c>
+      <c r="D335" s="3">
+        <v>45</v>
+      </c>
+      <c r="E335" s="3">
+        <v>46</v>
+      </c>
+      <c r="F335" s="3">
+        <v>48</v>
+      </c>
+      <c r="G335" s="3">
+        <v>50</v>
+      </c>
+      <c r="H335" s="3">
+        <v>1</v>
+      </c>
+      <c r="I335" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A336" s="2">
+        <v>335</v>
+      </c>
+      <c r="B336" s="3">
+        <v>1</v>
+      </c>
+      <c r="C336" s="3">
+        <v>4</v>
+      </c>
+      <c r="D336" s="3">
+        <v>15</v>
+      </c>
+      <c r="E336" s="3">
+        <v>16</v>
+      </c>
+      <c r="F336" s="3">
+        <v>41</v>
+      </c>
+      <c r="G336" s="3">
+        <v>50</v>
+      </c>
+      <c r="H336" s="3">
+        <v>2</v>
+      </c>
+      <c r="I336" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A337" s="2">
+        <v>336</v>
+      </c>
+      <c r="B337" s="3">
+        <v>13</v>
+      </c>
+      <c r="C337" s="3">
+        <v>32</v>
+      </c>
+      <c r="D337" s="3">
+        <v>33</v>
+      </c>
+      <c r="E337" s="3">
+        <v>35</v>
+      </c>
+      <c r="F337" s="3">
+        <v>42</v>
+      </c>
+      <c r="G337" s="3">
+        <v>47</v>
+      </c>
+      <c r="H337" s="3">
+        <v>3</v>
+      </c>
+      <c r="I337" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A338" s="2">
+        <v>337</v>
+      </c>
+      <c r="B338" s="3">
+        <v>3</v>
+      </c>
+      <c r="C338" s="3">
+        <v>18</v>
+      </c>
+      <c r="D338" s="3">
+        <v>27</v>
+      </c>
+      <c r="E338" s="3">
+        <v>29</v>
+      </c>
+      <c r="F338" s="3">
+        <v>34</v>
+      </c>
+      <c r="G338" s="3">
+        <v>43</v>
+      </c>
+      <c r="H338" s="3">
+        <v>2</v>
+      </c>
+      <c r="I338" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A339" s="2">
+        <v>338</v>
+      </c>
+      <c r="B339" s="3">
+        <v>3</v>
+      </c>
+      <c r="C339" s="3">
+        <v>5</v>
+      </c>
+      <c r="D339" s="3">
+        <v>6</v>
+      </c>
+      <c r="E339" s="3">
+        <v>10</v>
+      </c>
+      <c r="F339" s="3">
+        <v>16</v>
+      </c>
+      <c r="G339" s="3">
+        <v>25</v>
+      </c>
+      <c r="H339" s="3">
+        <v>4</v>
+      </c>
+      <c r="I339" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A340" s="2">
+        <v>339</v>
+      </c>
+      <c r="B340" s="3">
+        <v>15</v>
+      </c>
+      <c r="C340" s="3">
+        <v>27</v>
+      </c>
+      <c r="D340" s="3">
+        <v>32</v>
+      </c>
+      <c r="E340" s="3">
+        <v>40</v>
+      </c>
+      <c r="F340" s="3">
+        <v>41</v>
+      </c>
+      <c r="G340" s="3">
+        <v>42</v>
+      </c>
+      <c r="H340" s="3">
+        <v>4</v>
+      </c>
+      <c r="I340" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A341" s="2">
+        <v>340</v>
+      </c>
+      <c r="B341" s="3">
+        <v>24</v>
+      </c>
+      <c r="C341" s="3">
+        <v>31</v>
+      </c>
+      <c r="D341" s="3">
+        <v>35</v>
+      </c>
+      <c r="E341" s="3">
+        <v>40</v>
+      </c>
+      <c r="F341" s="3">
+        <v>41</v>
+      </c>
+      <c r="G341" s="3">
+        <v>42</v>
+      </c>
+      <c r="H341" s="3">
+        <v>5</v>
+      </c>
+      <c r="I341" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A342" s="2">
+        <v>341</v>
+      </c>
+      <c r="B342" s="3">
+        <v>1</v>
+      </c>
+      <c r="C342" s="3">
+        <v>18</v>
+      </c>
+      <c r="D342" s="3">
+        <v>21</v>
+      </c>
+      <c r="E342" s="3">
+        <v>38</v>
+      </c>
+      <c r="F342" s="3">
+        <v>41</v>
+      </c>
+      <c r="G342" s="3">
+        <v>50</v>
+      </c>
+      <c r="H342" s="3">
+        <v>2</v>
+      </c>
+      <c r="I342" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A343" s="2">
+        <v>342</v>
+      </c>
+      <c r="B343" s="3">
+        <v>6</v>
+      </c>
+      <c r="C343" s="3">
+        <v>9</v>
+      </c>
+      <c r="D343" s="3">
+        <v>20</v>
+      </c>
+      <c r="E343" s="3">
+        <v>40</v>
+      </c>
+      <c r="F343" s="3">
+        <v>41</v>
+      </c>
+      <c r="G343" s="3">
+        <v>43</v>
+      </c>
+      <c r="H343" s="3">
+        <v>1</v>
+      </c>
+      <c r="I343" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A344" s="2">
+        <v>343</v>
+      </c>
+      <c r="B344" s="3">
+        <v>1</v>
+      </c>
+      <c r="C344" s="3">
+        <v>16</v>
+      </c>
+      <c r="D344" s="3">
+        <v>17</v>
+      </c>
+      <c r="E344" s="3">
+        <v>26</v>
+      </c>
+      <c r="F344" s="3">
+        <v>34</v>
+      </c>
+      <c r="G344" s="3">
+        <v>50</v>
+      </c>
+      <c r="H344" s="3">
+        <v>1</v>
+      </c>
+      <c r="I344" s="3">
         <v>4</v>
       </c>
     </row>
@@ -10079,13 +10429,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10257,21 +10606,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10297,9 +10644,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050933A2-C2F7-4492-81E4-490E5F3224DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FED5A0-9042-4B4D-A1C3-D3463B20C9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59805" yWindow="2205" windowWidth="19485" windowHeight="18465" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="57405" yWindow="105" windowWidth="18675" windowHeight="12840" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="+ MILIONÁRIA" sheetId="12" r:id="rId1"/>
@@ -436,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2F70E5-30B2-4963-A61E-AD5ABF761887}">
-  <dimension ref="A1:I344"/>
+  <dimension ref="A1:I349"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.86328125" bestFit="1" customWidth="1"/>
@@ -10075,351 +10075,496 @@
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A333" s="2">
+      <c r="A333">
         <v>332</v>
       </c>
-      <c r="B333" s="3">
+      <c r="B333">
         <v>35</v>
       </c>
-      <c r="C333" s="3">
+      <c r="C333">
         <v>36</v>
       </c>
-      <c r="D333" s="3">
+      <c r="D333">
         <v>40</v>
       </c>
-      <c r="E333" s="3">
+      <c r="E333">
         <v>43</v>
       </c>
-      <c r="F333" s="3">
+      <c r="F333">
         <v>47</v>
       </c>
-      <c r="G333" s="3">
+      <c r="G333">
         <v>50</v>
       </c>
-      <c r="H333" s="3">
-        <v>4</v>
-      </c>
-      <c r="I333" s="3">
+      <c r="H333">
+        <v>4</v>
+      </c>
+      <c r="I333">
         <v>6</v>
       </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A334" s="2">
+      <c r="A334">
         <v>333</v>
       </c>
-      <c r="B334" s="3">
-        <v>1</v>
-      </c>
-      <c r="C334" s="3">
+      <c r="B334">
+        <v>1</v>
+      </c>
+      <c r="C334">
         <v>20</v>
       </c>
-      <c r="D334" s="3">
+      <c r="D334">
         <v>28</v>
       </c>
-      <c r="E334" s="3">
+      <c r="E334">
         <v>37</v>
       </c>
-      <c r="F334" s="3">
+      <c r="F334">
         <v>40</v>
       </c>
-      <c r="G334" s="3">
+      <c r="G334">
         <v>43</v>
       </c>
-      <c r="H334" s="3">
-        <v>2</v>
-      </c>
-      <c r="I334" s="3">
+      <c r="H334">
+        <v>2</v>
+      </c>
+      <c r="I334">
         <v>6</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A335" s="2">
+      <c r="A335">
         <v>334</v>
       </c>
-      <c r="B335" s="3">
+      <c r="B335">
         <v>25</v>
       </c>
-      <c r="C335" s="3">
+      <c r="C335">
         <v>44</v>
       </c>
-      <c r="D335" s="3">
+      <c r="D335">
         <v>45</v>
       </c>
-      <c r="E335" s="3">
+      <c r="E335">
         <v>46</v>
       </c>
-      <c r="F335" s="3">
+      <c r="F335">
         <v>48</v>
       </c>
-      <c r="G335" s="3">
+      <c r="G335">
         <v>50</v>
       </c>
-      <c r="H335" s="3">
-        <v>1</v>
-      </c>
-      <c r="I335" s="3">
+      <c r="H335">
+        <v>1</v>
+      </c>
+      <c r="I335">
         <v>5</v>
       </c>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A336" s="2">
+      <c r="A336">
         <v>335</v>
       </c>
-      <c r="B336" s="3">
-        <v>1</v>
-      </c>
-      <c r="C336" s="3">
-        <v>4</v>
-      </c>
-      <c r="D336" s="3">
+      <c r="B336">
+        <v>1</v>
+      </c>
+      <c r="C336">
+        <v>4</v>
+      </c>
+      <c r="D336">
         <v>15</v>
       </c>
-      <c r="E336" s="3">
+      <c r="E336">
         <v>16</v>
       </c>
-      <c r="F336" s="3">
+      <c r="F336">
         <v>41</v>
       </c>
-      <c r="G336" s="3">
+      <c r="G336">
         <v>50</v>
       </c>
-      <c r="H336" s="3">
-        <v>2</v>
-      </c>
-      <c r="I336" s="3">
+      <c r="H336">
+        <v>2</v>
+      </c>
+      <c r="I336">
         <v>5</v>
       </c>
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A337" s="2">
+      <c r="A337">
         <v>336</v>
       </c>
-      <c r="B337" s="3">
+      <c r="B337">
         <v>13</v>
       </c>
-      <c r="C337" s="3">
+      <c r="C337">
         <v>32</v>
       </c>
-      <c r="D337" s="3">
+      <c r="D337">
         <v>33</v>
       </c>
-      <c r="E337" s="3">
+      <c r="E337">
         <v>35</v>
       </c>
-      <c r="F337" s="3">
+      <c r="F337">
         <v>42</v>
       </c>
-      <c r="G337" s="3">
+      <c r="G337">
         <v>47</v>
       </c>
-      <c r="H337" s="3">
-        <v>3</v>
-      </c>
-      <c r="I337" s="3">
+      <c r="H337">
+        <v>3</v>
+      </c>
+      <c r="I337">
         <v>6</v>
       </c>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A338" s="2">
+      <c r="A338">
         <v>337</v>
       </c>
-      <c r="B338" s="3">
-        <v>3</v>
-      </c>
-      <c r="C338" s="3">
+      <c r="B338">
+        <v>3</v>
+      </c>
+      <c r="C338">
         <v>18</v>
       </c>
-      <c r="D338" s="3">
+      <c r="D338">
         <v>27</v>
       </c>
-      <c r="E338" s="3">
+      <c r="E338">
         <v>29</v>
       </c>
-      <c r="F338" s="3">
+      <c r="F338">
         <v>34</v>
       </c>
-      <c r="G338" s="3">
+      <c r="G338">
         <v>43</v>
       </c>
-      <c r="H338" s="3">
-        <v>2</v>
-      </c>
-      <c r="I338" s="3">
+      <c r="H338">
+        <v>2</v>
+      </c>
+      <c r="I338">
         <v>4</v>
       </c>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A339" s="2">
+      <c r="A339">
         <v>338</v>
       </c>
-      <c r="B339" s="3">
-        <v>3</v>
-      </c>
-      <c r="C339" s="3">
-        <v>5</v>
-      </c>
-      <c r="D339" s="3">
-        <v>6</v>
-      </c>
-      <c r="E339" s="3">
+      <c r="B339">
+        <v>3</v>
+      </c>
+      <c r="C339">
+        <v>5</v>
+      </c>
+      <c r="D339">
+        <v>6</v>
+      </c>
+      <c r="E339">
         <v>10</v>
       </c>
-      <c r="F339" s="3">
+      <c r="F339">
         <v>16</v>
       </c>
-      <c r="G339" s="3">
+      <c r="G339">
         <v>25</v>
       </c>
-      <c r="H339" s="3">
-        <v>4</v>
-      </c>
-      <c r="I339" s="3">
+      <c r="H339">
+        <v>4</v>
+      </c>
+      <c r="I339">
         <v>5</v>
       </c>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A340" s="2">
+      <c r="A340">
         <v>339</v>
       </c>
-      <c r="B340" s="3">
+      <c r="B340">
         <v>15</v>
       </c>
-      <c r="C340" s="3">
+      <c r="C340">
         <v>27</v>
       </c>
-      <c r="D340" s="3">
+      <c r="D340">
         <v>32</v>
       </c>
-      <c r="E340" s="3">
+      <c r="E340">
         <v>40</v>
       </c>
-      <c r="F340" s="3">
+      <c r="F340">
         <v>41</v>
       </c>
-      <c r="G340" s="3">
+      <c r="G340">
         <v>42</v>
       </c>
-      <c r="H340" s="3">
-        <v>4</v>
-      </c>
-      <c r="I340" s="3">
+      <c r="H340">
+        <v>4</v>
+      </c>
+      <c r="I340">
         <v>6</v>
       </c>
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A341" s="2">
+      <c r="A341">
         <v>340</v>
       </c>
-      <c r="B341" s="3">
+      <c r="B341">
         <v>24</v>
       </c>
-      <c r="C341" s="3">
+      <c r="C341">
         <v>31</v>
       </c>
-      <c r="D341" s="3">
+      <c r="D341">
         <v>35</v>
       </c>
-      <c r="E341" s="3">
+      <c r="E341">
         <v>40</v>
       </c>
-      <c r="F341" s="3">
+      <c r="F341">
         <v>41</v>
       </c>
-      <c r="G341" s="3">
+      <c r="G341">
         <v>42</v>
       </c>
-      <c r="H341" s="3">
-        <v>5</v>
-      </c>
-      <c r="I341" s="3">
+      <c r="H341">
+        <v>5</v>
+      </c>
+      <c r="I341">
         <v>6</v>
       </c>
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A342" s="2">
+      <c r="A342">
         <v>341</v>
       </c>
-      <c r="B342" s="3">
-        <v>1</v>
-      </c>
-      <c r="C342" s="3">
+      <c r="B342">
+        <v>1</v>
+      </c>
+      <c r="C342">
         <v>18</v>
       </c>
-      <c r="D342" s="3">
+      <c r="D342">
         <v>21</v>
       </c>
-      <c r="E342" s="3">
+      <c r="E342">
         <v>38</v>
       </c>
-      <c r="F342" s="3">
+      <c r="F342">
         <v>41</v>
       </c>
-      <c r="G342" s="3">
+      <c r="G342">
         <v>50</v>
       </c>
-      <c r="H342" s="3">
-        <v>2</v>
-      </c>
-      <c r="I342" s="3">
+      <c r="H342">
+        <v>2</v>
+      </c>
+      <c r="I342">
         <v>5</v>
       </c>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A343" s="2">
+      <c r="A343">
         <v>342</v>
       </c>
-      <c r="B343" s="3">
-        <v>6</v>
-      </c>
-      <c r="C343" s="3">
+      <c r="B343">
+        <v>6</v>
+      </c>
+      <c r="C343">
         <v>9</v>
       </c>
-      <c r="D343" s="3">
+      <c r="D343">
         <v>20</v>
       </c>
-      <c r="E343" s="3">
+      <c r="E343">
         <v>40</v>
       </c>
-      <c r="F343" s="3">
+      <c r="F343">
         <v>41</v>
       </c>
-      <c r="G343" s="3">
+      <c r="G343">
         <v>43</v>
       </c>
-      <c r="H343" s="3">
-        <v>1</v>
-      </c>
-      <c r="I343" s="3">
+      <c r="H343">
+        <v>1</v>
+      </c>
+      <c r="I343">
         <v>4</v>
       </c>
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A344" s="2">
+      <c r="A344">
         <v>343</v>
       </c>
-      <c r="B344" s="3">
-        <v>1</v>
-      </c>
-      <c r="C344" s="3">
+      <c r="B344">
+        <v>1</v>
+      </c>
+      <c r="C344">
         <v>16</v>
       </c>
-      <c r="D344" s="3">
+      <c r="D344">
         <v>17</v>
       </c>
-      <c r="E344" s="3">
+      <c r="E344">
         <v>26</v>
       </c>
-      <c r="F344" s="3">
+      <c r="F344">
         <v>34</v>
       </c>
-      <c r="G344" s="3">
+      <c r="G344">
         <v>50</v>
       </c>
-      <c r="H344" s="3">
-        <v>1</v>
-      </c>
-      <c r="I344" s="3">
-        <v>4</v>
+      <c r="H344">
+        <v>1</v>
+      </c>
+      <c r="I344">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A345" s="2">
+        <v>344</v>
+      </c>
+      <c r="B345" s="3">
+        <v>3</v>
+      </c>
+      <c r="C345" s="3">
+        <v>4</v>
+      </c>
+      <c r="D345" s="3">
+        <v>11</v>
+      </c>
+      <c r="E345" s="3">
+        <v>14</v>
+      </c>
+      <c r="F345" s="3">
+        <v>16</v>
+      </c>
+      <c r="G345" s="3">
+        <v>29</v>
+      </c>
+      <c r="H345" s="3">
+        <v>1</v>
+      </c>
+      <c r="I345" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A346" s="2">
+        <v>345</v>
+      </c>
+      <c r="B346" s="3">
+        <v>19</v>
+      </c>
+      <c r="C346" s="3">
+        <v>20</v>
+      </c>
+      <c r="D346" s="3">
+        <v>25</v>
+      </c>
+      <c r="E346" s="3">
+        <v>27</v>
+      </c>
+      <c r="F346" s="3">
+        <v>38</v>
+      </c>
+      <c r="G346" s="3">
+        <v>41</v>
+      </c>
+      <c r="H346" s="3">
+        <v>1</v>
+      </c>
+      <c r="I346" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A347" s="2">
+        <v>346</v>
+      </c>
+      <c r="B347" s="3">
+        <v>1</v>
+      </c>
+      <c r="C347" s="3">
+        <v>18</v>
+      </c>
+      <c r="D347" s="3">
+        <v>21</v>
+      </c>
+      <c r="E347" s="3">
+        <v>24</v>
+      </c>
+      <c r="F347" s="3">
+        <v>37</v>
+      </c>
+      <c r="G347" s="3">
+        <v>44</v>
+      </c>
+      <c r="H347" s="3">
+        <v>3</v>
+      </c>
+      <c r="I347" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A348" s="2">
+        <v>347</v>
+      </c>
+      <c r="B348" s="3">
+        <v>3</v>
+      </c>
+      <c r="C348" s="3">
+        <v>6</v>
+      </c>
+      <c r="D348" s="3">
+        <v>25</v>
+      </c>
+      <c r="E348" s="3">
+        <v>28</v>
+      </c>
+      <c r="F348" s="3">
+        <v>31</v>
+      </c>
+      <c r="G348" s="3">
+        <v>48</v>
+      </c>
+      <c r="H348" s="3">
+        <v>2</v>
+      </c>
+      <c r="I348" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A349" s="2">
+        <v>348</v>
+      </c>
+      <c r="B349" s="3">
+        <v>6</v>
+      </c>
+      <c r="C349" s="3">
+        <v>14</v>
+      </c>
+      <c r="D349" s="3">
+        <v>21</v>
+      </c>
+      <c r="E349" s="3">
+        <v>24</v>
+      </c>
+      <c r="F349" s="3">
+        <v>44</v>
+      </c>
+      <c r="G349" s="3">
+        <v>49</v>
+      </c>
+      <c r="H349" s="3">
+        <v>4</v>
+      </c>
+      <c r="I349" s="3">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -10429,12 +10574,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10606,19 +10752,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10644,12 +10792,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FED5A0-9042-4B4D-A1C3-D3463B20C9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95DDA069-90B0-4B69-8C93-9541D3AC6A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57405" yWindow="105" windowWidth="18675" windowHeight="12840" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="66855" yWindow="810" windowWidth="18675" windowHeight="12840" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="+ MILIONÁRIA" sheetId="12" r:id="rId1"/>
@@ -109,13 +109,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -436,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2F70E5-30B2-4963-A61E-AD5ABF761887}">
-  <dimension ref="A1:I349"/>
+  <dimension ref="A1:I350"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.86328125" bestFit="1" customWidth="1"/>
@@ -10423,148 +10421,177 @@
       </c>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A345" s="2">
+      <c r="A345">
         <v>344</v>
       </c>
-      <c r="B345" s="3">
-        <v>3</v>
-      </c>
-      <c r="C345" s="3">
-        <v>4</v>
-      </c>
-      <c r="D345" s="3">
+      <c r="B345">
+        <v>3</v>
+      </c>
+      <c r="C345">
+        <v>4</v>
+      </c>
+      <c r="D345">
         <v>11</v>
       </c>
-      <c r="E345" s="3">
+      <c r="E345">
         <v>14</v>
       </c>
-      <c r="F345" s="3">
+      <c r="F345">
         <v>16</v>
       </c>
-      <c r="G345" s="3">
+      <c r="G345">
         <v>29</v>
       </c>
-      <c r="H345" s="3">
-        <v>1</v>
-      </c>
-      <c r="I345" s="3">
+      <c r="H345">
+        <v>1</v>
+      </c>
+      <c r="I345">
         <v>5</v>
       </c>
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A346" s="2">
+      <c r="A346">
         <v>345</v>
       </c>
-      <c r="B346" s="3">
+      <c r="B346">
         <v>19</v>
       </c>
-      <c r="C346" s="3">
+      <c r="C346">
         <v>20</v>
       </c>
-      <c r="D346" s="3">
+      <c r="D346">
         <v>25</v>
       </c>
-      <c r="E346" s="3">
+      <c r="E346">
         <v>27</v>
       </c>
-      <c r="F346" s="3">
+      <c r="F346">
         <v>38</v>
       </c>
-      <c r="G346" s="3">
+      <c r="G346">
         <v>41</v>
       </c>
-      <c r="H346" s="3">
-        <v>1</v>
-      </c>
-      <c r="I346" s="3">
+      <c r="H346">
+        <v>1</v>
+      </c>
+      <c r="I346">
         <v>4</v>
       </c>
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A347" s="2">
+      <c r="A347">
         <v>346</v>
       </c>
-      <c r="B347" s="3">
-        <v>1</v>
-      </c>
-      <c r="C347" s="3">
+      <c r="B347">
+        <v>1</v>
+      </c>
+      <c r="C347">
         <v>18</v>
       </c>
-      <c r="D347" s="3">
+      <c r="D347">
         <v>21</v>
       </c>
-      <c r="E347" s="3">
+      <c r="E347">
         <v>24</v>
       </c>
-      <c r="F347" s="3">
+      <c r="F347">
         <v>37</v>
       </c>
-      <c r="G347" s="3">
+      <c r="G347">
         <v>44</v>
       </c>
-      <c r="H347" s="3">
-        <v>3</v>
-      </c>
-      <c r="I347" s="3">
+      <c r="H347">
+        <v>3</v>
+      </c>
+      <c r="I347">
         <v>4</v>
       </c>
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A348" s="2">
+      <c r="A348">
         <v>347</v>
       </c>
-      <c r="B348" s="3">
-        <v>3</v>
-      </c>
-      <c r="C348" s="3">
-        <v>6</v>
-      </c>
-      <c r="D348" s="3">
+      <c r="B348">
+        <v>3</v>
+      </c>
+      <c r="C348">
+        <v>6</v>
+      </c>
+      <c r="D348">
         <v>25</v>
       </c>
-      <c r="E348" s="3">
+      <c r="E348">
         <v>28</v>
       </c>
-      <c r="F348" s="3">
+      <c r="F348">
         <v>31</v>
       </c>
-      <c r="G348" s="3">
+      <c r="G348">
         <v>48</v>
       </c>
-      <c r="H348" s="3">
-        <v>2</v>
-      </c>
-      <c r="I348" s="3">
+      <c r="H348">
+        <v>2</v>
+      </c>
+      <c r="I348">
         <v>5</v>
       </c>
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A349" s="2">
+      <c r="A349">
         <v>348</v>
       </c>
-      <c r="B349" s="3">
-        <v>6</v>
-      </c>
-      <c r="C349" s="3">
+      <c r="B349">
+        <v>6</v>
+      </c>
+      <c r="C349">
         <v>14</v>
       </c>
-      <c r="D349" s="3">
+      <c r="D349">
         <v>21</v>
       </c>
-      <c r="E349" s="3">
+      <c r="E349">
         <v>24</v>
       </c>
-      <c r="F349" s="3">
+      <c r="F349">
         <v>44</v>
       </c>
-      <c r="G349" s="3">
+      <c r="G349">
         <v>49</v>
       </c>
-      <c r="H349" s="3">
-        <v>4</v>
-      </c>
-      <c r="I349" s="3">
-        <v>5</v>
+      <c r="H349">
+        <v>4</v>
+      </c>
+      <c r="I349">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A350">
+        <v>349</v>
+      </c>
+      <c r="B350">
+        <v>12</v>
+      </c>
+      <c r="C350">
+        <v>15</v>
+      </c>
+      <c r="D350">
+        <v>21</v>
+      </c>
+      <c r="E350">
+        <v>36</v>
+      </c>
+      <c r="F350">
+        <v>37</v>
+      </c>
+      <c r="G350">
+        <v>41</v>
+      </c>
+      <c r="H350">
+        <v>2</v>
+      </c>
+      <c r="I350">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -10574,13 +10601,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10752,21 +10778,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10792,9 +10816,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95DDA069-90B0-4B69-8C93-9541D3AC6A4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BF0CAE-2D1C-4003-AEFC-AEBF6C01A6C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="66855" yWindow="810" windowWidth="18675" windowHeight="12840" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="58035" yWindow="7860" windowWidth="18885" windowHeight="6255" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="+ MILIONÁRIA" sheetId="12" r:id="rId1"/>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2F70E5-30B2-4963-A61E-AD5ABF761887}">
-  <dimension ref="A1:I350"/>
+  <dimension ref="A1:I353"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.86328125" bestFit="1" customWidth="1"/>
@@ -10594,6 +10594,93 @@
         <v>6</v>
       </c>
     </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A351">
+        <v>350</v>
+      </c>
+      <c r="B351">
+        <v>7</v>
+      </c>
+      <c r="C351">
+        <v>18</v>
+      </c>
+      <c r="D351">
+        <v>25</v>
+      </c>
+      <c r="E351">
+        <v>30</v>
+      </c>
+      <c r="F351">
+        <v>42</v>
+      </c>
+      <c r="G351">
+        <v>45</v>
+      </c>
+      <c r="H351">
+        <v>5</v>
+      </c>
+      <c r="I351">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A352">
+        <v>351</v>
+      </c>
+      <c r="B352">
+        <v>5</v>
+      </c>
+      <c r="C352">
+        <v>8</v>
+      </c>
+      <c r="D352">
+        <v>23</v>
+      </c>
+      <c r="E352">
+        <v>29</v>
+      </c>
+      <c r="F352">
+        <v>34</v>
+      </c>
+      <c r="G352">
+        <v>42</v>
+      </c>
+      <c r="H352">
+        <v>5</v>
+      </c>
+      <c r="I352">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A353">
+        <v>352</v>
+      </c>
+      <c r="B353">
+        <v>1</v>
+      </c>
+      <c r="C353">
+        <v>10</v>
+      </c>
+      <c r="D353">
+        <v>13</v>
+      </c>
+      <c r="E353">
+        <v>23</v>
+      </c>
+      <c r="F353">
+        <v>24</v>
+      </c>
+      <c r="G353">
+        <v>40</v>
+      </c>
+      <c r="H353">
+        <v>5</v>
+      </c>
+      <c r="I353">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10601,15 +10688,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -10777,6 +10855,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -10788,14 +10875,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD255BF4-F3C2-4BEE-8F0D-D649B10487B5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10815,6 +10894,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BF0CAE-2D1C-4003-AEFC-AEBF6C01A6C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA169E6A-E9C9-4DD8-964E-F8D135DD2A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58035" yWindow="7860" windowWidth="18885" windowHeight="6255" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="21300" windowHeight="10559" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="+ MILIONÁRIA" sheetId="12" r:id="rId1"/>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2F70E5-30B2-4963-A61E-AD5ABF761887}">
-  <dimension ref="A1:I353"/>
+  <dimension ref="A1:I366"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.86328125" bestFit="1" customWidth="1"/>
@@ -10681,6 +10681,383 @@
         <v>6</v>
       </c>
     </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A354">
+        <v>353</v>
+      </c>
+      <c r="B354">
+        <v>8</v>
+      </c>
+      <c r="C354">
+        <v>19</v>
+      </c>
+      <c r="D354">
+        <v>24</v>
+      </c>
+      <c r="E354">
+        <v>27</v>
+      </c>
+      <c r="F354">
+        <v>35</v>
+      </c>
+      <c r="G354">
+        <v>36</v>
+      </c>
+      <c r="H354">
+        <v>2</v>
+      </c>
+      <c r="I354">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A355">
+        <v>354</v>
+      </c>
+      <c r="B355">
+        <v>4</v>
+      </c>
+      <c r="C355">
+        <v>11</v>
+      </c>
+      <c r="D355">
+        <v>14</v>
+      </c>
+      <c r="E355">
+        <v>32</v>
+      </c>
+      <c r="F355">
+        <v>35</v>
+      </c>
+      <c r="G355">
+        <v>40</v>
+      </c>
+      <c r="H355">
+        <v>3</v>
+      </c>
+      <c r="I355">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A356">
+        <v>355</v>
+      </c>
+      <c r="B356">
+        <v>6</v>
+      </c>
+      <c r="C356">
+        <v>7</v>
+      </c>
+      <c r="D356">
+        <v>10</v>
+      </c>
+      <c r="E356">
+        <v>30</v>
+      </c>
+      <c r="F356">
+        <v>40</v>
+      </c>
+      <c r="G356">
+        <v>47</v>
+      </c>
+      <c r="H356">
+        <v>1</v>
+      </c>
+      <c r="I356">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A357">
+        <v>356</v>
+      </c>
+      <c r="B357">
+        <v>1</v>
+      </c>
+      <c r="C357">
+        <v>5</v>
+      </c>
+      <c r="D357">
+        <v>9</v>
+      </c>
+      <c r="E357">
+        <v>22</v>
+      </c>
+      <c r="F357">
+        <v>25</v>
+      </c>
+      <c r="G357">
+        <v>28</v>
+      </c>
+      <c r="H357">
+        <v>1</v>
+      </c>
+      <c r="I357">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A358">
+        <v>357</v>
+      </c>
+      <c r="B358">
+        <v>7</v>
+      </c>
+      <c r="C358">
+        <v>8</v>
+      </c>
+      <c r="D358">
+        <v>10</v>
+      </c>
+      <c r="E358">
+        <v>23</v>
+      </c>
+      <c r="F358">
+        <v>38</v>
+      </c>
+      <c r="G358">
+        <v>42</v>
+      </c>
+      <c r="H358">
+        <v>1</v>
+      </c>
+      <c r="I358">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A359">
+        <v>358</v>
+      </c>
+      <c r="B359">
+        <v>1</v>
+      </c>
+      <c r="C359">
+        <v>6</v>
+      </c>
+      <c r="D359">
+        <v>12</v>
+      </c>
+      <c r="E359">
+        <v>18</v>
+      </c>
+      <c r="F359">
+        <v>22</v>
+      </c>
+      <c r="G359">
+        <v>42</v>
+      </c>
+      <c r="H359">
+        <v>5</v>
+      </c>
+      <c r="I359">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A360">
+        <v>359</v>
+      </c>
+      <c r="B360">
+        <v>1</v>
+      </c>
+      <c r="C360">
+        <v>8</v>
+      </c>
+      <c r="D360">
+        <v>10</v>
+      </c>
+      <c r="E360">
+        <v>12</v>
+      </c>
+      <c r="F360">
+        <v>22</v>
+      </c>
+      <c r="G360">
+        <v>30</v>
+      </c>
+      <c r="H360">
+        <v>1</v>
+      </c>
+      <c r="I360">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A361">
+        <v>360</v>
+      </c>
+      <c r="B361">
+        <v>4</v>
+      </c>
+      <c r="C361">
+        <v>7</v>
+      </c>
+      <c r="D361">
+        <v>15</v>
+      </c>
+      <c r="E361">
+        <v>20</v>
+      </c>
+      <c r="F361">
+        <v>23</v>
+      </c>
+      <c r="G361">
+        <v>34</v>
+      </c>
+      <c r="H361">
+        <v>3</v>
+      </c>
+      <c r="I361">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A362">
+        <v>361</v>
+      </c>
+      <c r="B362">
+        <v>10</v>
+      </c>
+      <c r="C362">
+        <v>21</v>
+      </c>
+      <c r="D362">
+        <v>22</v>
+      </c>
+      <c r="E362">
+        <v>31</v>
+      </c>
+      <c r="F362">
+        <v>33</v>
+      </c>
+      <c r="G362">
+        <v>35</v>
+      </c>
+      <c r="H362">
+        <v>1</v>
+      </c>
+      <c r="I362">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A363">
+        <v>362</v>
+      </c>
+      <c r="B363">
+        <v>4</v>
+      </c>
+      <c r="C363">
+        <v>13</v>
+      </c>
+      <c r="D363">
+        <v>28</v>
+      </c>
+      <c r="E363">
+        <v>31</v>
+      </c>
+      <c r="F363">
+        <v>40</v>
+      </c>
+      <c r="G363">
+        <v>47</v>
+      </c>
+      <c r="H363">
+        <v>3</v>
+      </c>
+      <c r="I363">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A364">
+        <v>363</v>
+      </c>
+      <c r="B364">
+        <v>7</v>
+      </c>
+      <c r="C364">
+        <v>12</v>
+      </c>
+      <c r="D364">
+        <v>22</v>
+      </c>
+      <c r="E364">
+        <v>25</v>
+      </c>
+      <c r="F364">
+        <v>36</v>
+      </c>
+      <c r="G364">
+        <v>38</v>
+      </c>
+      <c r="H364">
+        <v>3</v>
+      </c>
+      <c r="I364">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A365">
+        <v>364</v>
+      </c>
+      <c r="B365">
+        <v>12</v>
+      </c>
+      <c r="C365">
+        <v>20</v>
+      </c>
+      <c r="D365">
+        <v>23</v>
+      </c>
+      <c r="E365">
+        <v>29</v>
+      </c>
+      <c r="F365">
+        <v>32</v>
+      </c>
+      <c r="G365">
+        <v>48</v>
+      </c>
+      <c r="H365">
+        <v>3</v>
+      </c>
+      <c r="I365">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A366">
+        <v>365</v>
+      </c>
+      <c r="B366">
+        <v>4</v>
+      </c>
+      <c r="C366">
+        <v>6</v>
+      </c>
+      <c r="D366">
+        <v>10</v>
+      </c>
+      <c r="E366">
+        <v>27</v>
+      </c>
+      <c r="F366">
+        <v>32</v>
+      </c>
+      <c r="G366">
+        <v>44</v>
+      </c>
+      <c r="H366">
+        <v>2</v>
+      </c>
+      <c r="I366">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10688,6 +11065,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -10855,15 +11241,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -10875,6 +11252,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD255BF4-F3C2-4BEE-8F0D-D649B10487B5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10894,14 +11279,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA169E6A-E9C9-4DD8-964E-F8D135DD2A22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8552D0B5-15F1-47DD-849E-A6F2C5EC2EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="21300" windowHeight="10559" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="59070" yWindow="1035" windowWidth="12750" windowHeight="15165" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="+ MILIONÁRIA" sheetId="12" r:id="rId1"/>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2F70E5-30B2-4963-A61E-AD5ABF761887}">
-  <dimension ref="A1:I366"/>
+  <dimension ref="A1:I367"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.86328125" bestFit="1" customWidth="1"/>
@@ -11058,6 +11058,35 @@
         <v>6</v>
       </c>
     </row>
+    <row r="367" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A367">
+        <v>366</v>
+      </c>
+      <c r="B367">
+        <v>1</v>
+      </c>
+      <c r="C367">
+        <v>11</v>
+      </c>
+      <c r="D367">
+        <v>14</v>
+      </c>
+      <c r="E367">
+        <v>22</v>
+      </c>
+      <c r="F367">
+        <v>25</v>
+      </c>
+      <c r="G367">
+        <v>37</v>
+      </c>
+      <c r="H367">
+        <v>2</v>
+      </c>
+      <c r="I367">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11065,12 +11094,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11242,19 +11272,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11280,12 +11312,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8552D0B5-15F1-47DD-849E-A6F2C5EC2EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4E8C83-1D3A-4FF2-A783-CAFD1B5F6566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59070" yWindow="1035" windowWidth="12750" windowHeight="15165" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="57555" yWindow="150" windowWidth="19515" windowHeight="14565" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="+ MILIONÁRIA" sheetId="12" r:id="rId1"/>
@@ -109,11 +109,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2F70E5-30B2-4963-A61E-AD5ABF761887}">
-  <dimension ref="A1:I367"/>
+  <dimension ref="A1:I368"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.86328125" bestFit="1" customWidth="1"/>
@@ -11087,6 +11088,35 @@
         <v>5</v>
       </c>
     </row>
+    <row r="368" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A368">
+        <v>367</v>
+      </c>
+      <c r="B368" s="2">
+        <v>6</v>
+      </c>
+      <c r="C368" s="2">
+        <v>20</v>
+      </c>
+      <c r="D368" s="2">
+        <v>29</v>
+      </c>
+      <c r="E368" s="2">
+        <v>38</v>
+      </c>
+      <c r="F368" s="2">
+        <v>45</v>
+      </c>
+      <c r="G368" s="2">
+        <v>48</v>
+      </c>
+      <c r="H368" s="2">
+        <v>1</v>
+      </c>
+      <c r="I368" s="2">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11094,13 +11124,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11272,21 +11301,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11312,9 +11339,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4E8C83-1D3A-4FF2-A783-CAFD1B5F6566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36783B81-4A35-4C3F-946B-89D88D5F8F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57555" yWindow="150" windowWidth="19515" windowHeight="14565" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="66390" yWindow="870" windowWidth="19770" windowHeight="11130" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="+ MILIONÁRIA" sheetId="12" r:id="rId1"/>
@@ -109,11 +109,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2F70E5-30B2-4963-A61E-AD5ABF761887}">
-  <dimension ref="A1:I368"/>
+  <dimension ref="A1:I370"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.86328125" bestFit="1" customWidth="1"/>
@@ -11092,29 +11093,87 @@
       <c r="A368">
         <v>367</v>
       </c>
-      <c r="B368" s="2">
-        <v>6</v>
-      </c>
-      <c r="C368" s="2">
+      <c r="B368">
+        <v>6</v>
+      </c>
+      <c r="C368">
         <v>20</v>
       </c>
-      <c r="D368" s="2">
+      <c r="D368">
         <v>29</v>
       </c>
-      <c r="E368" s="2">
+      <c r="E368">
         <v>38</v>
       </c>
-      <c r="F368" s="2">
+      <c r="F368">
         <v>45</v>
       </c>
-      <c r="G368" s="2">
+      <c r="G368">
         <v>48</v>
       </c>
-      <c r="H368" s="2">
-        <v>1</v>
-      </c>
-      <c r="I368" s="2">
-        <v>6</v>
+      <c r="H368">
+        <v>1</v>
+      </c>
+      <c r="I368">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A369" s="2">
+        <v>368</v>
+      </c>
+      <c r="B369" s="3">
+        <v>1</v>
+      </c>
+      <c r="C369" s="3">
+        <v>2</v>
+      </c>
+      <c r="D369" s="3">
+        <v>20</v>
+      </c>
+      <c r="E369" s="3">
+        <v>28</v>
+      </c>
+      <c r="F369" s="3">
+        <v>42</v>
+      </c>
+      <c r="G369" s="3">
+        <v>48</v>
+      </c>
+      <c r="H369" s="3">
+        <v>4</v>
+      </c>
+      <c r="I369" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A370" s="2">
+        <v>369</v>
+      </c>
+      <c r="B370" s="3">
+        <v>4</v>
+      </c>
+      <c r="C370" s="3">
+        <v>6</v>
+      </c>
+      <c r="D370" s="3">
+        <v>20</v>
+      </c>
+      <c r="E370" s="3">
+        <v>22</v>
+      </c>
+      <c r="F370" s="3">
+        <v>26</v>
+      </c>
+      <c r="G370" s="3">
+        <v>41</v>
+      </c>
+      <c r="H370" s="3">
+        <v>1</v>
+      </c>
+      <c r="I370" s="3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -11124,12 +11183,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11301,19 +11361,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11339,12 +11401,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36783B81-4A35-4C3F-946B-89D88D5F8F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D84B8BE-A95C-4878-8630-220EC97BD2DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="66390" yWindow="870" windowWidth="19770" windowHeight="11130" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="61245" yWindow="870" windowWidth="19770" windowHeight="11130" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="+ MILIONÁRIA" sheetId="12" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Concurso</t>
   </si>
@@ -61,6 +61,9 @@
   </si>
   <si>
     <t>Trevo1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -109,13 +112,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -436,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F2F70E5-30B2-4963-A61E-AD5ABF761887}">
-  <dimension ref="A1:I370"/>
+  <dimension ref="A1:I394"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.86328125" bestFit="1" customWidth="1"/>
@@ -11119,61 +11120,95 @@
       </c>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A369" s="2">
+      <c r="A369">
         <v>368</v>
       </c>
-      <c r="B369" s="3">
-        <v>1</v>
-      </c>
-      <c r="C369" s="3">
-        <v>2</v>
-      </c>
-      <c r="D369" s="3">
+      <c r="B369">
+        <v>1</v>
+      </c>
+      <c r="C369">
+        <v>2</v>
+      </c>
+      <c r="D369">
         <v>20</v>
       </c>
-      <c r="E369" s="3">
+      <c r="E369">
         <v>28</v>
       </c>
-      <c r="F369" s="3">
+      <c r="F369">
         <v>42</v>
       </c>
-      <c r="G369" s="3">
+      <c r="G369">
         <v>48</v>
       </c>
-      <c r="H369" s="3">
-        <v>4</v>
-      </c>
-      <c r="I369" s="3">
+      <c r="H369">
+        <v>4</v>
+      </c>
+      <c r="I369">
         <v>6</v>
       </c>
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A370" s="2">
+      <c r="A370">
         <v>369</v>
       </c>
-      <c r="B370" s="3">
-        <v>4</v>
-      </c>
-      <c r="C370" s="3">
-        <v>6</v>
-      </c>
-      <c r="D370" s="3">
+      <c r="B370">
+        <v>4</v>
+      </c>
+      <c r="C370">
+        <v>6</v>
+      </c>
+      <c r="D370">
         <v>20</v>
       </c>
-      <c r="E370" s="3">
+      <c r="E370">
         <v>22</v>
       </c>
-      <c r="F370" s="3">
+      <c r="F370">
         <v>26</v>
       </c>
-      <c r="G370" s="3">
+      <c r="G370">
         <v>41</v>
       </c>
-      <c r="H370" s="3">
-        <v>1</v>
-      </c>
-      <c r="I370" s="3">
-        <v>2</v>
+      <c r="H370">
+        <v>1</v>
+      </c>
+      <c r="I370">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A371">
+        <v>370</v>
+      </c>
+      <c r="B371">
+        <v>9</v>
+      </c>
+      <c r="C371">
+        <v>16</v>
+      </c>
+      <c r="D371">
+        <v>17</v>
+      </c>
+      <c r="E371">
+        <v>20</v>
+      </c>
+      <c r="F371">
+        <v>48</v>
+      </c>
+      <c r="G371">
+        <v>49</v>
+      </c>
+      <c r="H371">
+        <v>1</v>
+      </c>
+      <c r="I371">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="394" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B394" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -11183,13 +11218,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11361,21 +11395,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11401,9 +11433,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D84B8BE-A95C-4878-8630-220EC97BD2DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{109C7282-A66D-43C2-B23F-D86DE8209ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61245" yWindow="870" windowWidth="19770" windowHeight="11130" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="59415" yWindow="135" windowWidth="26985" windowHeight="7695" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="+ MILIONÁRIA" sheetId="12" r:id="rId1"/>
@@ -112,11 +112,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11206,6 +11208,64 @@
         <v>4</v>
       </c>
     </row>
+    <row r="372" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A372" s="2">
+        <v>371</v>
+      </c>
+      <c r="B372" s="3">
+        <v>5</v>
+      </c>
+      <c r="C372" s="3">
+        <v>13</v>
+      </c>
+      <c r="D372" s="3">
+        <v>35</v>
+      </c>
+      <c r="E372" s="3">
+        <v>40</v>
+      </c>
+      <c r="F372" s="3">
+        <v>42</v>
+      </c>
+      <c r="G372" s="3">
+        <v>49</v>
+      </c>
+      <c r="H372" s="3">
+        <v>2</v>
+      </c>
+      <c r="I372" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A373" s="2">
+        <v>372</v>
+      </c>
+      <c r="B373" s="3">
+        <v>3</v>
+      </c>
+      <c r="C373" s="3">
+        <v>13</v>
+      </c>
+      <c r="D373" s="3">
+        <v>14</v>
+      </c>
+      <c r="E373" s="3">
+        <v>28</v>
+      </c>
+      <c r="F373" s="3">
+        <v>30</v>
+      </c>
+      <c r="G373" s="3">
+        <v>49</v>
+      </c>
+      <c r="H373" s="3">
+        <v>1</v>
+      </c>
+      <c r="I373" s="3">
+        <v>5</v>
+      </c>
+    </row>
     <row r="394" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B394" t="s">
         <v>9</v>
@@ -11218,12 +11278,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11395,19 +11456,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11433,12 +11496,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{109C7282-A66D-43C2-B23F-D86DE8209ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE623A7-52AB-4A04-ABAD-D8DE6013DF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59415" yWindow="135" windowWidth="26985" windowHeight="7695" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="25447" windowHeight="9345" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="+ MILIONÁRIA" sheetId="12" r:id="rId1"/>
@@ -11209,61 +11209,148 @@
       </c>
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A372" s="2">
+      <c r="A372">
         <v>371</v>
       </c>
-      <c r="B372" s="3">
-        <v>5</v>
-      </c>
-      <c r="C372" s="3">
+      <c r="B372">
+        <v>5</v>
+      </c>
+      <c r="C372">
         <v>13</v>
       </c>
-      <c r="D372" s="3">
+      <c r="D372">
         <v>35</v>
       </c>
-      <c r="E372" s="3">
+      <c r="E372">
         <v>40</v>
       </c>
-      <c r="F372" s="3">
+      <c r="F372">
         <v>42</v>
       </c>
-      <c r="G372" s="3">
+      <c r="G372">
         <v>49</v>
       </c>
-      <c r="H372" s="3">
-        <v>2</v>
-      </c>
-      <c r="I372" s="3">
+      <c r="H372">
+        <v>2</v>
+      </c>
+      <c r="I372">
         <v>3</v>
       </c>
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A373" s="2">
+      <c r="A373">
         <v>372</v>
       </c>
-      <c r="B373" s="3">
-        <v>3</v>
-      </c>
-      <c r="C373" s="3">
+      <c r="B373">
+        <v>3</v>
+      </c>
+      <c r="C373">
         <v>13</v>
       </c>
-      <c r="D373" s="3">
+      <c r="D373">
         <v>14</v>
       </c>
-      <c r="E373" s="3">
+      <c r="E373">
         <v>28</v>
       </c>
-      <c r="F373" s="3">
+      <c r="F373">
         <v>30</v>
       </c>
-      <c r="G373" s="3">
+      <c r="G373">
         <v>49</v>
       </c>
-      <c r="H373" s="3">
-        <v>1</v>
-      </c>
-      <c r="I373" s="3">
-        <v>5</v>
+      <c r="H373">
+        <v>1</v>
+      </c>
+      <c r="I373">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A374" s="2">
+        <v>373</v>
+      </c>
+      <c r="B374" s="3">
+        <v>10</v>
+      </c>
+      <c r="C374" s="3">
+        <v>17</v>
+      </c>
+      <c r="D374" s="3">
+        <v>19</v>
+      </c>
+      <c r="E374" s="3">
+        <v>37</v>
+      </c>
+      <c r="F374" s="3">
+        <v>40</v>
+      </c>
+      <c r="G374" s="3">
+        <v>50</v>
+      </c>
+      <c r="H374" s="3">
+        <v>2</v>
+      </c>
+      <c r="I374" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A375" s="2">
+        <v>374</v>
+      </c>
+      <c r="B375" s="3">
+        <v>2</v>
+      </c>
+      <c r="C375" s="3">
+        <v>4</v>
+      </c>
+      <c r="D375" s="3">
+        <v>8</v>
+      </c>
+      <c r="E375" s="3">
+        <v>28</v>
+      </c>
+      <c r="F375" s="3">
+        <v>30</v>
+      </c>
+      <c r="G375" s="3">
+        <v>37</v>
+      </c>
+      <c r="H375" s="3">
+        <v>1</v>
+      </c>
+      <c r="I375" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A376" s="2">
+        <v>375</v>
+      </c>
+      <c r="B376" s="3">
+        <v>2</v>
+      </c>
+      <c r="C376" s="3">
+        <v>6</v>
+      </c>
+      <c r="D376" s="3">
+        <v>15</v>
+      </c>
+      <c r="E376" s="3">
+        <v>19</v>
+      </c>
+      <c r="F376" s="3">
+        <v>25</v>
+      </c>
+      <c r="G376" s="3">
+        <v>29</v>
+      </c>
+      <c r="H376" s="3">
+        <v>3</v>
+      </c>
+      <c r="I376" s="3">
+        <v>4</v>
       </c>
     </row>
     <row r="394" spans="2:2" x14ac:dyDescent="0.45">
@@ -11278,13 +11365,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11456,21 +11542,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11496,9 +11580,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE623A7-52AB-4A04-ABAD-D8DE6013DF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBF0F91-2F06-466D-9ACE-DBC1CB5B65A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="25447" windowHeight="9345" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="405" yWindow="248" windowWidth="25680" windowHeight="13455" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="+ MILIONÁRIA" sheetId="12" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>Concurso</t>
   </si>
@@ -112,13 +112,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11267,90 +11265,127 @@
       </c>
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A374" s="2">
+      <c r="A374">
         <v>373</v>
       </c>
-      <c r="B374" s="3">
+      <c r="B374">
         <v>10</v>
       </c>
-      <c r="C374" s="3">
+      <c r="C374">
         <v>17</v>
       </c>
-      <c r="D374" s="3">
+      <c r="D374">
         <v>19</v>
       </c>
-      <c r="E374" s="3">
+      <c r="E374">
         <v>37</v>
       </c>
-      <c r="F374" s="3">
+      <c r="F374">
         <v>40</v>
       </c>
-      <c r="G374" s="3">
+      <c r="G374">
         <v>50</v>
       </c>
-      <c r="H374" s="3">
-        <v>2</v>
-      </c>
-      <c r="I374" s="3">
+      <c r="H374">
+        <v>2</v>
+      </c>
+      <c r="I374">
         <v>3</v>
       </c>
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A375" s="2">
+      <c r="A375">
         <v>374</v>
       </c>
-      <c r="B375" s="3">
-        <v>2</v>
-      </c>
-      <c r="C375" s="3">
-        <v>4</v>
-      </c>
-      <c r="D375" s="3">
+      <c r="B375">
+        <v>2</v>
+      </c>
+      <c r="C375">
+        <v>4</v>
+      </c>
+      <c r="D375">
         <v>8</v>
       </c>
-      <c r="E375" s="3">
+      <c r="E375">
         <v>28</v>
       </c>
-      <c r="F375" s="3">
+      <c r="F375">
         <v>30</v>
       </c>
-      <c r="G375" s="3">
+      <c r="G375">
         <v>37</v>
       </c>
-      <c r="H375" s="3">
-        <v>1</v>
-      </c>
-      <c r="I375" s="3">
+      <c r="H375">
+        <v>1</v>
+      </c>
+      <c r="I375">
         <v>4</v>
       </c>
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A376" s="2">
+      <c r="A376">
         <v>375</v>
       </c>
-      <c r="B376" s="3">
-        <v>2</v>
-      </c>
-      <c r="C376" s="3">
-        <v>6</v>
-      </c>
-      <c r="D376" s="3">
+      <c r="B376">
+        <v>2</v>
+      </c>
+      <c r="C376">
+        <v>6</v>
+      </c>
+      <c r="D376">
         <v>15</v>
       </c>
-      <c r="E376" s="3">
+      <c r="E376">
         <v>19</v>
       </c>
-      <c r="F376" s="3">
+      <c r="F376">
         <v>25</v>
       </c>
-      <c r="G376" s="3">
+      <c r="G376">
         <v>29</v>
       </c>
-      <c r="H376" s="3">
-        <v>3</v>
-      </c>
-      <c r="I376" s="3">
-        <v>4</v>
+      <c r="H376">
+        <v>3</v>
+      </c>
+      <c r="I376">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A377">
+        <v>376</v>
+      </c>
+      <c r="B377">
+        <v>1</v>
+      </c>
+      <c r="C377">
+        <v>2</v>
+      </c>
+      <c r="D377">
+        <v>35</v>
+      </c>
+      <c r="E377">
+        <v>38</v>
+      </c>
+      <c r="F377">
+        <v>40</v>
+      </c>
+      <c r="G377">
+        <v>45</v>
+      </c>
+      <c r="H377">
+        <v>3</v>
+      </c>
+      <c r="I377">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="H382" t="s">
+        <v>9</v>
+      </c>
+      <c r="I382" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="394" spans="2:2" x14ac:dyDescent="0.45">
@@ -11365,12 +11400,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11542,19 +11578,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11580,12 +11618,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBF0F91-2F06-466D-9ACE-DBC1CB5B65A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E678B82-18A5-4CEA-B27B-E94C8486F553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="405" yWindow="248" windowWidth="25680" windowHeight="13455" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="2318" yWindow="525" windowWidth="25545" windowHeight="10118" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="+ MILIONÁRIA" sheetId="12" r:id="rId1"/>
@@ -11380,6 +11380,35 @@
         <v>4</v>
       </c>
     </row>
+    <row r="378" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A378">
+        <v>377</v>
+      </c>
+      <c r="B378">
+        <v>1</v>
+      </c>
+      <c r="C378">
+        <v>14</v>
+      </c>
+      <c r="D378">
+        <v>15</v>
+      </c>
+      <c r="E378">
+        <v>21</v>
+      </c>
+      <c r="F378">
+        <v>30</v>
+      </c>
+      <c r="G378">
+        <v>47</v>
+      </c>
+      <c r="H378">
+        <v>4</v>
+      </c>
+      <c r="I378">
+        <v>6</v>
+      </c>
+    </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.45">
       <c r="H382" t="s">
         <v>9</v>
@@ -11400,13 +11429,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11578,21 +11606,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11618,9 +11644,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E678B82-18A5-4CEA-B27B-E94C8486F553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9920E97-353F-449B-A60A-F533FBF5EF1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2318" yWindow="525" windowWidth="25545" windowHeight="10118" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="-158" yWindow="1132" windowWidth="25546" windowHeight="10118" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="+ MILIONÁRIA" sheetId="12" r:id="rId1"/>
@@ -11409,6 +11409,35 @@
         <v>6</v>
       </c>
     </row>
+    <row r="379" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A379">
+        <v>378</v>
+      </c>
+      <c r="B379">
+        <v>7</v>
+      </c>
+      <c r="C379">
+        <v>8</v>
+      </c>
+      <c r="D379">
+        <v>9</v>
+      </c>
+      <c r="E379">
+        <v>15</v>
+      </c>
+      <c r="F379">
+        <v>46</v>
+      </c>
+      <c r="G379">
+        <v>49</v>
+      </c>
+      <c r="H379">
+        <v>2</v>
+      </c>
+      <c r="I379">
+        <v>5</v>
+      </c>
+    </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.45">
       <c r="H382" t="s">
         <v>9</v>
@@ -11429,12 +11458,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11606,19 +11636,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11644,12 +11676,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9920E97-353F-449B-A60A-F533FBF5EF1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D7D94C-6A66-4F90-ACF3-2FE13FB5875C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-158" yWindow="1132" windowWidth="25546" windowHeight="10118" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="3135" yWindow="2078" windowWidth="23610" windowHeight="9420" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="+ MILIONÁRIA" sheetId="12" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Concurso</t>
   </si>
@@ -112,11 +112,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11438,12 +11440,91 @@
         <v>5</v>
       </c>
     </row>
+    <row r="380" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A380" s="2">
+        <v>379</v>
+      </c>
+      <c r="B380" s="3">
+        <v>4</v>
+      </c>
+      <c r="C380" s="3">
+        <v>7</v>
+      </c>
+      <c r="D380" s="3">
+        <v>14</v>
+      </c>
+      <c r="E380" s="3">
+        <v>28</v>
+      </c>
+      <c r="F380" s="3">
+        <v>38</v>
+      </c>
+      <c r="G380" s="3">
+        <v>47</v>
+      </c>
+      <c r="H380" s="3">
+        <v>2</v>
+      </c>
+      <c r="I380" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A381" s="2">
+        <v>380</v>
+      </c>
+      <c r="B381" s="3">
+        <v>3</v>
+      </c>
+      <c r="C381" s="3">
+        <v>37</v>
+      </c>
+      <c r="D381" s="3">
+        <v>38</v>
+      </c>
+      <c r="E381" s="3">
+        <v>41</v>
+      </c>
+      <c r="F381" s="3">
+        <v>42</v>
+      </c>
+      <c r="G381" s="3">
+        <v>43</v>
+      </c>
+      <c r="H381" s="3">
+        <v>4</v>
+      </c>
+      <c r="I381" s="3">
+        <v>6</v>
+      </c>
+    </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="H382" t="s">
-        <v>9</v>
-      </c>
-      <c r="I382" t="s">
-        <v>9</v>
+      <c r="A382" s="2">
+        <v>381</v>
+      </c>
+      <c r="B382" s="3">
+        <v>23</v>
+      </c>
+      <c r="C382" s="3">
+        <v>32</v>
+      </c>
+      <c r="D382" s="3">
+        <v>33</v>
+      </c>
+      <c r="E382" s="3">
+        <v>38</v>
+      </c>
+      <c r="F382" s="3">
+        <v>45</v>
+      </c>
+      <c r="G382" s="3">
+        <v>46</v>
+      </c>
+      <c r="H382" s="3">
+        <v>3</v>
+      </c>
+      <c r="I382" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="394" spans="2:2" x14ac:dyDescent="0.45">
@@ -11458,13 +11539,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11636,21 +11716,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11676,9 +11754,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Milionária_edt.xlsx
+++ b/LoteriasExcel/Milionária_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D7D94C-6A66-4F90-ACF3-2FE13FB5875C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADCF8AF-73E9-4607-8E21-8592F1EE9458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3135" yWindow="2078" windowWidth="23610" windowHeight="9420" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="3450" yWindow="1365" windowWidth="23610" windowHeight="9420" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="+ MILIONÁRIA" sheetId="12" r:id="rId1"/>
@@ -11441,90 +11441,119 @@
       </c>
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A380" s="2">
+      <c r="A380">
         <v>379</v>
       </c>
-      <c r="B380" s="3">
-        <v>4</v>
-      </c>
-      <c r="C380" s="3">
+      <c r="B380">
+        <v>4</v>
+      </c>
+      <c r="C380">
         <v>7</v>
       </c>
-      <c r="D380" s="3">
+      <c r="D380">
         <v>14</v>
       </c>
-      <c r="E380" s="3">
+      <c r="E380">
         <v>28</v>
       </c>
-      <c r="F380" s="3">
+      <c r="F380">
         <v>38</v>
       </c>
-      <c r="G380" s="3">
+      <c r="G380">
         <v>47</v>
       </c>
-      <c r="H380" s="3">
-        <v>2</v>
-      </c>
-      <c r="I380" s="3">
+      <c r="H380">
+        <v>2</v>
+      </c>
+      <c r="I380">
         <v>6</v>
       </c>
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A381" s="2">
+      <c r="A381">
         <v>380</v>
       </c>
-      <c r="B381" s="3">
-        <v>3</v>
-      </c>
-      <c r="C381" s="3">
+      <c r="B381">
+        <v>3</v>
+      </c>
+      <c r="C381">
         <v>37</v>
       </c>
-      <c r="D381" s="3">
+      <c r="D381">
         <v>38</v>
       </c>
-      <c r="E381" s="3">
+      <c r="E381">
         <v>41</v>
       </c>
-      <c r="F381" s="3">
+      <c r="F381">
         <v>42</v>
       </c>
-      <c r="G381" s="3">
+      <c r="G381">
         <v>43</v>
       </c>
-      <c r="H381" s="3">
-        <v>4</v>
-      </c>
-      <c r="I381" s="3">
+      <c r="H381">
+        <v>4</v>
+      </c>
+      <c r="I381">
         <v>6</v>
       </c>
     </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A382" s="2">
+      <c r="A382">
         <v>381</v>
       </c>
-      <c r="B382" s="3">
+      <c r="B382">
         <v>23</v>
       </c>
-      <c r="C382" s="3">
+      <c r="C382">
         <v>32</v>
       </c>
-      <c r="D382" s="3">
+      <c r="D382">
         <v>33</v>
       </c>
-      <c r="E382" s="3">
+      <c r="E382">
         <v>38</v>
       </c>
-      <c r="F382" s="3">
+      <c r="F382">
         <v>45</v>
       </c>
-      <c r="G382" s="3">
+      <c r="G382">
         <v>46</v>
       </c>
-      <c r="H382" s="3">
-        <v>3</v>
-      </c>
-      <c r="I382" s="3">
-        <v>5</v>
+      <c r="H382">
+        <v>3</v>
+      </c>
+      <c r="I382">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A383" s="2">
+        <v>382</v>
+      </c>
+      <c r="B383" s="3">
+        <v>10</v>
+      </c>
+      <c r="C383" s="3">
+        <v>17</v>
+      </c>
+      <c r="D383" s="3">
+        <v>23</v>
+      </c>
+      <c r="E383" s="3">
+        <v>30</v>
+      </c>
+      <c r="F383" s="3">
+        <v>44</v>
+      </c>
+      <c r="G383" s="3">
+        <v>48</v>
+      </c>
+      <c r="H383" s="3">
+        <v>4</v>
+      </c>
+      <c r="I383" s="3">
+        <v>6</v>
       </c>
     </row>
     <row r="394" spans="2:2" x14ac:dyDescent="0.45">
@@ -11539,12 +11568,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11716,19 +11746,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-07-21T04:06:33+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11754,12 +11786,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5937A41-16C2-4E59-B938-0AB818017E0A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498C8BED-ADD0-4229-BCAE-F34B21F201A9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>